--- a/api-django/characteristics_export.xlsx
+++ b/api-django/characteristics_export.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diare\Desktop\sp2-ics-ipb-npgrl\api-django\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046BAFD1-FFB1-4F80-A2F9-8B45BB4AEB80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A700BE68-72CA-4644-9EA0-982C20807734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="646" firstSheet="32" activeTab="35" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AkapulkoCharacteristics" sheetId="1" r:id="rId1"/>
@@ -55,12 +55,25 @@
     <sheet name="YamCharacteristics" sheetId="40" r:id="rId40"/>
     <sheet name="YerbabuenaCharacteristics" sheetId="41" r:id="rId41"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="1434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2384" uniqueCount="1436">
   <si>
     <t>accession_number</t>
   </si>
@@ -4362,19 +4375,30 @@
   </si>
   <si>
     <t>pubescence_density_of_corolla</t>
+  </si>
+  <si>
+    <t>GB72520</t>
+  </si>
+  <si>
+    <t>red</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="DM Sans"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4397,8 +4421,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10086,8 +10111,11 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
-  <dimension ref="A1:CP1"/>
+  <dimension ref="A1:CP2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="8" max="8" width="36.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:94" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -10371,6 +10399,23 @@
       </c>
       <c r="CP1" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:94" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
